--- a/questions_12.xlsx
+++ b/questions_12.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="95">
   <si>
     <t>question</t>
   </si>
@@ -53,289 +53,262 @@
     <t>C</t>
   </si>
   <si>
-    <t>चुम्बकीय फ्लक्स (Magnetic Flux) का SI मात्रक क्या है?</t>
-  </si>
-  <si>
-    <t>टेस्ला</t>
-  </si>
-  <si>
-    <t>वेबर</t>
-  </si>
-  <si>
     <t>हेनरी</t>
   </si>
   <si>
-    <t>गॉस</t>
-  </si>
-  <si>
-    <t>फैराडे के विद्युत चुम्बकीय प्रेरण के नियम के अनुसार, प्रेरित वि.वा.बल (Induced EMF) किसके समानुपाती होता है?</t>
-  </si>
-  <si>
-    <t>चुम्बकीय फ्लक्स</t>
-  </si>
-  <si>
-    <t>चुम्बकीय क्षेत्र की तीव्रता</t>
-  </si>
-  <si>
-    <t>चुम्बकीय फ्लक्स में परिवर्तन की दर</t>
-  </si>
-  <si>
-    <t>परिपथ के प्रतिरोध</t>
-  </si>
-  <si>
-    <t>लेन्ज का नियम किस भौतिक राशि के संरक्षण नियम पर आधारित है?</t>
-  </si>
-  <si>
-    <t>आवेश</t>
-  </si>
-  <si>
-    <t>द्रव्यमान</t>
-  </si>
-  <si>
-    <t>ऊर्जा</t>
-  </si>
-  <si>
-    <t>संवेग</t>
-  </si>
-  <si>
-    <t>स्वप्रेरकत्व (Self-Inductance) का SI मात्रक क्या है?</t>
-  </si>
-  <si>
-    <t>ओम-सेकंड</t>
-  </si>
-  <si>
-    <t>एक गतिमान चालक छड़ में प्रेरित वि.वा.बल (Motional EMF) का मान क्या होता है?</t>
-  </si>
-  <si>
-    <t>Bvl</t>
-  </si>
-  <si>
-    <t>B²vl</t>
-  </si>
-  <si>
-    <t>Bv/l</t>
-  </si>
-  <si>
-    <t>Bl/v</t>
-  </si>
-  <si>
-    <t>जब किसी कुण्डली में 1 A/s की दर से धारा परिवर्तित होने पर उसमें 1 V का वि.वा.बल प्रेरित होता है, तो उसका प्रेरकत्व होगा:</t>
-  </si>
-  <si>
-    <t>1 F</t>
-  </si>
-  <si>
-    <t>1 H</t>
-  </si>
-  <si>
-    <t>1 Ω</t>
-  </si>
-  <si>
-    <t>1 Wb</t>
-  </si>
-  <si>
-    <t>भंवर धाराएँ (Eddy Currents) निम्नलिखित में से किसमें उत्पन्न होती हैं?</t>
-  </si>
-  <si>
-    <t>केवल पतले तारों में</t>
-  </si>
-  <si>
-    <t>धातु के ठोस टुकड़ों में</t>
-  </si>
-  <si>
-    <t>केवल द्रवों में</t>
-  </si>
-  <si>
-    <t>कुचालकों में</t>
-  </si>
-  <si>
-    <t>किसी प्रेरक (Inductor) में संचित चुम्बकीय ऊर्जा का सूत्र क्या है?</t>
-  </si>
-  <si>
-    <t>(1/2) LI²</t>
-  </si>
-  <si>
-    <t>LI²</t>
-  </si>
-  <si>
-    <t>(1/2) L²I</t>
-  </si>
-  <si>
-    <t>L/I²</t>
-  </si>
-  <si>
-    <t>ट्रान्सफॉर्मर की क्रोड (Core) को पटलित (Laminated) क्यों बनाया जाता है?</t>
-  </si>
-  <si>
-    <t>ताम्र हानि कम करने के लिए</t>
-  </si>
-  <si>
-    <t>भंवर धारा हानि कम करने के लिए</t>
-  </si>
-  <si>
-    <t>हिस्टेरेसिस हानि कम करने के लिए</t>
-  </si>
-  <si>
-    <t>फ्लक्स क्षरण रोकने के लिए</t>
-  </si>
-  <si>
-    <t>लेन्ज के नियम के अनुसार प्रेरित धारा की दिशा हमेशा ऐसी होती है कि वह:</t>
-  </si>
-  <si>
-    <t>फ्लक्स वृद्धि का समर्थन करती है</t>
-  </si>
-  <si>
-    <t>उस कारण का विरोध करती है जिससे वह उत्पन्न हुई है</t>
-  </si>
-  <si>
-    <t>हमेशा नियत रहती है</t>
-  </si>
-  <si>
-    <t>धारा के परिमाण पर निर्भर नहीं करती</t>
-  </si>
-  <si>
-    <t>दो कुण्डलियों के बीच पारस्परिक प्रेरकत्व (Mutual Inductance) किस पर निर्भर करता है?</t>
-  </si>
-  <si>
-    <t>कुण्डलियों की ज्यामिति पर</t>
-  </si>
-  <si>
-    <t>दोनों के बीच की दूरी पर</t>
-  </si>
-  <si>
-    <t>फेरों की संख्या पर</t>
-  </si>
-  <si>
-    <t>उपरोक्त सभी पर</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>AC जनरेटर (प्रत्यावर्ती धारा जनित्र) किस सिद्धांत पर कार्य करता है?</t>
-  </si>
-  <si>
-    <t>जूल का तापन नियम</t>
-  </si>
-  <si>
-    <t>विद्युत चुम्बकीय प्रेरण</t>
-  </si>
-  <si>
-    <t>प्रकाश विद्युत प्रभाव</t>
-  </si>
-  <si>
-    <t>पास्कल का नियम</t>
-  </si>
-  <si>
-    <t>चुम्बकीय फ्लक्स घनत्व (Magnetic Flux Density) का मात्रक क्या है?</t>
-  </si>
-  <si>
-    <t>एम्पीयर-मीटर</t>
-  </si>
-  <si>
-    <t>एक परिनालिका (Solenoid) का स्वप्रेरकत्व फेरों की संख्या (N) के साथ कैसे संबंधित है?</t>
-  </si>
-  <si>
-    <t>L ∝ N</t>
-  </si>
-  <si>
-    <t>L ∝ N²</t>
-  </si>
-  <si>
-    <t>L ∝ √N</t>
-  </si>
-  <si>
-    <t>L ∝ 1/N</t>
-  </si>
-  <si>
-    <t>भंवर धाराओं के प्रभाव को रोकने या कम करने के लिए धातुओं में क्या किया जाता है?</t>
-  </si>
-  <si>
-    <t>धातु को गर्म किया जाता है</t>
-  </si>
-  <si>
-    <t>खांचे (Slots) काटे जाते हैं</t>
-  </si>
-  <si>
-    <t>सतह पर लेप लगाया जाता है</t>
-  </si>
-  <si>
-    <t>धारा का मान बढ़ाया जाता है</t>
-  </si>
-  <si>
-    <t>जब किसी परिपथ में धारा शून्य से अधिकतम मान तक बढ़ती है, तो प्रेरित वि.वा.बल की प्रवृत्ति क्या होती है?</t>
-  </si>
-  <si>
-    <t>धारा को बढ़ाना</t>
-  </si>
-  <si>
-    <t>धारा की वृद्धि का विरोध करना</t>
-  </si>
-  <si>
-    <t>धारा को तुरंत शून्य करना</t>
-  </si>
-  <si>
-    <t>कोई प्रभाव नहीं डालना</t>
-  </si>
-  <si>
-    <t>फ्लेमिंग के दाएँ हाथ का नियम (Right-Hand Rule) किसकी दिशा ज्ञात करने के लिए उपयोग किया जाता है?</t>
-  </si>
-  <si>
-    <t>प्रेरित धारा</t>
-  </si>
-  <si>
-    <t>चुम्बकीय बल</t>
-  </si>
-  <si>
-    <t>चुम्बकीय क्षेत्र रेखाएँ</t>
-  </si>
-  <si>
-    <t>घूर्णन अक्ष</t>
-  </si>
-  <si>
-    <t>यदि किसी कुण्डली में फेरों की संख्या दोगुनी कर दी जाए, तो उसका स्वप्रेरकत्व कितना गुना हो जाएगा?</t>
-  </si>
-  <si>
-    <t>2 गुना</t>
-  </si>
-  <si>
-    <t>4 गुना</t>
-  </si>
-  <si>
-    <t>आधा</t>
-  </si>
-  <si>
-    <t>अपरिवर्तित</t>
-  </si>
-  <si>
-    <t>चुम्बकीय फ्लक्स कैसी राशि है?</t>
-  </si>
-  <si>
-    <t>सदिश राशि</t>
-  </si>
-  <si>
-    <t>अदिश राशि</t>
-  </si>
-  <si>
-    <t>न सदिश न अदिश</t>
-  </si>
-  <si>
-    <t>प्रदिश (Tensor)</t>
-  </si>
-  <si>
-    <t>एकसमान चुम्बकीय क्षेत्र में कोणीय वेग ω से घूर्णन करती N फेरों वाली कुण्डली में अधिकतम प्रेरित वि.वा.बल का मान होता है:</t>
-  </si>
-  <si>
-    <t>NABω</t>
-  </si>
-  <si>
-    <t>NAB</t>
-  </si>
-  <si>
-    <t>NAB/ω</t>
-  </si>
-  <si>
-    <t>N²ABω</t>
+    <t>भारत में घरों में आपूर्ति की जाने वाली प्रत्यावर्ती धारा (AC) की आवृत्ति कितनी होती है?</t>
+  </si>
+  <si>
+    <t>60 Hz</t>
+  </si>
+  <si>
+    <t>50 Hz</t>
+  </si>
+  <si>
+    <t>100 Hz</t>
+  </si>
+  <si>
+    <t>0 Hz</t>
+  </si>
+  <si>
+    <t>प्रत्यावर्ती धारा के शिखर मान (I0​) और वर्ग माध्य मूल मान (Irms​) में क्या संबंध होता है?</t>
+  </si>
+  <si>
+    <t>Irms​=I0​/2​</t>
+  </si>
+  <si>
+    <t>Irms​=2​I0​</t>
+  </si>
+  <si>
+    <t>Irms​=2I0​</t>
+  </si>
+  <si>
+    <t>Irms​=I0​/2</t>
+  </si>
+  <si>
+    <t>एक पूरे चक्र (Full cycle) में प्रत्यावर्ती धारा का औसत मान (Average value) कितना होता है?</t>
+  </si>
+  <si>
+    <t>शिखर मान के बराबर</t>
+  </si>
+  <si>
+    <t>अनंत</t>
+  </si>
+  <si>
+    <t>शून्य</t>
+  </si>
+  <si>
+    <t>I0​/2​</t>
+  </si>
+  <si>
+    <t>केवल धारिता (Capacitor) वाले AC परिपथ में धारा और वोल्टेज के बीच कलान्तर कितना होता है?</t>
+  </si>
+  <si>
+    <t>धारा वोल्टेज से 90∘ आगे होती है</t>
+  </si>
+  <si>
+    <t>वोल्टेज धारा से 90∘ आगे होता है</t>
+  </si>
+  <si>
+    <t>दोनों समान कला में होते हैं</t>
+  </si>
+  <si>
+    <t>कलान्तर 180∘ होता है</t>
+  </si>
+  <si>
+    <t>प्रेरणिक प्रतिघात (Inductive Reactance, XL​) का सूत्र क्या है?</t>
+  </si>
+  <si>
+    <t>ω/L</t>
+  </si>
+  <si>
+    <t>1/(ωL)</t>
+  </si>
+  <si>
+    <t>ωL</t>
+  </si>
+  <si>
+    <t>L/ω</t>
+  </si>
+  <si>
+    <t>दिष्ट धारा (DC) के लिए एक संधारित्र (Capacitor) का प्रतिघात (XC​) कितना होता है?</t>
+  </si>
+  <si>
+    <t>1 ओम</t>
+  </si>
+  <si>
+    <t>आवृत्ति पर निर्भर</t>
+  </si>
+  <si>
+    <t>श्रेणी LCR परिपथ में अनुनाद (Resonance) की स्थिति में परिपथ की प्रतिबाधा (Impedance, Z) किसके बराबर होती है?</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>XL​+XC​</t>
+  </si>
+  <si>
+    <t>श्रेणी LCR परिपथ की अनुनादी आवृत्ति (fr​) का सूत्र क्या होता है?</t>
+  </si>
+  <si>
+    <t>2πLC​1​</t>
+  </si>
+  <si>
+    <t>LC​2π​</t>
+  </si>
+  <si>
+    <t>2πLC​​</t>
+  </si>
+  <si>
+    <t>LC1​</t>
+  </si>
+  <si>
+    <t>शक्ति गुणांक (Power Factor, cosϕ) का अधिकतम मान कितना हो सकता है?</t>
+  </si>
+  <si>
+    <t>2​</t>
+  </si>
+  <si>
+    <t>शुद्ध प्रेरकत्व (Pure Inductance) वाले AC परिपथ में क्षय होने वाली औसत शक्ति कितनी होती है?</t>
+  </si>
+  <si>
+    <t>Vrms​Irms​</t>
+  </si>
+  <si>
+    <t>(1/2)Vrms​Irms​</t>
+  </si>
+  <si>
+    <t>वाटहीन धारा (Wattless current) प्रवाहित होने के लिए धारा और वोल्टेज के बीच कलान्तर कितना होना चाहिए?</t>
+  </si>
+  <si>
+    <t>0∘</t>
+  </si>
+  <si>
+    <t>45∘</t>
+  </si>
+  <si>
+    <t>90∘</t>
+  </si>
+  <si>
+    <t>180∘</t>
+  </si>
+  <si>
+    <t>प्रत्यावर्ती धारा को मापने वाले मीटर (AC Ammeter) किस प्रभाव पर आधारित होते हैं?</t>
+  </si>
+  <si>
+    <t>चुम्बकीय प्रभाव</t>
+  </si>
+  <si>
+    <t>रासायनिक प्रभाव</t>
+  </si>
+  <si>
+    <t>ऊष्मीय प्रभाव (तप्त तार सिद्धांत)</t>
+  </si>
+  <si>
+    <t>स्थिरवैद्युत प्रभाव</t>
+  </si>
+  <si>
+    <t>ट्रान्सफॉर्मर किस सिद्धांत पर कार्य करता है?</t>
+  </si>
+  <si>
+    <t>स्वप्रेरण</t>
+  </si>
+  <si>
+    <t>पारस्परिक प्रेरण (Mutual Induction)</t>
+  </si>
+  <si>
+    <t>भंवर धारा प्रभाव</t>
+  </si>
+  <si>
+    <t>सीबेक प्रभाव</t>
+  </si>
+  <si>
+    <t>एक अपचायी (Step-down) ट्रान्सफॉर्मर में क्या होता है?</t>
+  </si>
+  <si>
+    <t>Vs​&gt;Vp​</t>
+  </si>
+  <si>
+    <t>Ns​&gt;Np​</t>
+  </si>
+  <si>
+    <t>Vs​&lt;Vp​</t>
+  </si>
+  <si>
+    <t>Is​&lt;Ip​</t>
+  </si>
+  <si>
+    <t>प्रतिबाधा (Impedance) और प्रतिघात (Reactance) का SI मात्रक क्या है?</t>
+  </si>
+  <si>
+    <t>फैराड</t>
+  </si>
+  <si>
+    <t>ओम</t>
+  </si>
+  <si>
+    <t>वाट</t>
+  </si>
+  <si>
+    <t>किसी LCR परिपथ में गुणवत्ता गुणांक (Q-factor) की परिभाषा क्या है?</t>
+  </si>
+  <si>
+    <t>Rω0​L​</t>
+  </si>
+  <si>
+    <t>ω0​LR​</t>
+  </si>
+  <si>
+    <t>LRω0​​</t>
+  </si>
+  <si>
+    <t>यदि AC वोल्टेज समीकरण V=2002​sin(100πt) है, तो इसका वर्ग माध्य मूल (RMS) वोल्टेज कितना होगा?</t>
+  </si>
+  <si>
+    <t>200 V</t>
+  </si>
+  <si>
+    <t>100 V</t>
+  </si>
+  <si>
+    <t>282.8 V</t>
+  </si>
+  <si>
+    <t>400 V</t>
+  </si>
+  <si>
+    <t>प्रत्यावर्ती धारा को दिष्ट धारा (DC) में परिवर्तित करने वाली युक्ति को क्या कहते हैं?</t>
+  </si>
+  <si>
+    <t>इन्वर्टर</t>
+  </si>
+  <si>
+    <t>दिष्टकारी (Rectifier)</t>
+  </si>
+  <si>
+    <t>ट्रान्सफॉर्मर</t>
+  </si>
+  <si>
+    <t>प्रेरक कुण्डली</t>
+  </si>
+  <si>
+    <t>चोक कुण्डली (Choke Coil) का उपयोग AC परिपथ में किसके लिए किया जाता है?</t>
+  </si>
+  <si>
+    <t>धारा बढ़ाने के लिए</t>
+  </si>
+  <si>
+    <t>ऊर्जा हानि किए बिना धारा नियंत्रित करने के लिए</t>
+  </si>
+  <si>
+    <t>वोल्टेज बढ़ाने के लिए</t>
+  </si>
+  <si>
+    <t>आवृत्ति बदलने के लिए</t>
+  </si>
+  <si>
+    <t>एक शुद्ध प्रतिरोधक (Purely Resistive) AC परिपथ में शक्ति गुणांक (Power factor) का मान कितना होता है?</t>
   </si>
 </sst>
 </file>
@@ -400,13 +373,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -711,147 +687,147 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="89" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="76.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="176.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:6" ht="89" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
         <v>41</v>
       </c>
@@ -875,240 +851,240 @@
       <c r="A10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="176.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="64" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" s="2" t="s">
+    <row r="15" spans="1:6" ht="89" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C15" s="2" t="s">
+    <row r="16" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="2" t="s">
+      <c r="E17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="176.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="51.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="176.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>103</v>
+        <v>94</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/questions_12.xlsx
+++ b/questions_12.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="96">
   <si>
     <t>question</t>
   </si>
@@ -71,21 +71,6 @@
     <t>0 Hz</t>
   </si>
   <si>
-    <t>प्रत्यावर्ती धारा के शिखर मान (I0​) और वर्ग माध्य मूल मान (Irms​) में क्या संबंध होता है?</t>
-  </si>
-  <si>
-    <t>Irms​=I0​/2​</t>
-  </si>
-  <si>
-    <t>Irms​=2​I0​</t>
-  </si>
-  <si>
-    <t>Irms​=2I0​</t>
-  </si>
-  <si>
-    <t>Irms​=I0​/2</t>
-  </si>
-  <si>
     <t>एक पूरे चक्र (Full cycle) में प्रत्यावर्ती धारा का औसत मान (Average value) कितना होता है?</t>
   </si>
   <si>
@@ -98,42 +83,15 @@
     <t>शून्य</t>
   </si>
   <si>
-    <t>I0​/2​</t>
-  </si>
-  <si>
     <t>केवल धारिता (Capacitor) वाले AC परिपथ में धारा और वोल्टेज के बीच कलान्तर कितना होता है?</t>
   </si>
   <si>
-    <t>धारा वोल्टेज से 90∘ आगे होती है</t>
-  </si>
-  <si>
-    <t>वोल्टेज धारा से 90∘ आगे होता है</t>
-  </si>
-  <si>
     <t>दोनों समान कला में होते हैं</t>
   </si>
   <si>
-    <t>कलान्तर 180∘ होता है</t>
-  </si>
-  <si>
-    <t>प्रेरणिक प्रतिघात (Inductive Reactance, XL​) का सूत्र क्या है?</t>
-  </si>
-  <si>
-    <t>ω/L</t>
-  </si>
-  <si>
-    <t>1/(ωL)</t>
-  </si>
-  <si>
     <t>ωL</t>
   </si>
   <si>
-    <t>L/ω</t>
-  </si>
-  <si>
-    <t>दिष्ट धारा (DC) के लिए एक संधारित्र (Capacitor) का प्रतिघात (XC​) कितना होता है?</t>
-  </si>
-  <si>
     <t>1 ओम</t>
   </si>
   <si>
@@ -146,54 +104,12 @@
     <t>R</t>
   </si>
   <si>
-    <t>XL​+XC​</t>
-  </si>
-  <si>
-    <t>श्रेणी LCR परिपथ की अनुनादी आवृत्ति (fr​) का सूत्र क्या होता है?</t>
-  </si>
-  <si>
-    <t>2πLC​1​</t>
-  </si>
-  <si>
-    <t>LC​2π​</t>
-  </si>
-  <si>
-    <t>2πLC​​</t>
-  </si>
-  <si>
-    <t>LC1​</t>
-  </si>
-  <si>
-    <t>शक्ति गुणांक (Power Factor, cosϕ) का अधिकतम मान कितना हो सकता है?</t>
-  </si>
-  <si>
-    <t>2​</t>
-  </si>
-  <si>
     <t>शुद्ध प्रेरकत्व (Pure Inductance) वाले AC परिपथ में क्षय होने वाली औसत शक्ति कितनी होती है?</t>
   </si>
   <si>
-    <t>Vrms​Irms​</t>
-  </si>
-  <si>
-    <t>(1/2)Vrms​Irms​</t>
-  </si>
-  <si>
     <t>वाटहीन धारा (Wattless current) प्रवाहित होने के लिए धारा और वोल्टेज के बीच कलान्तर कितना होना चाहिए?</t>
   </si>
   <si>
-    <t>0∘</t>
-  </si>
-  <si>
-    <t>45∘</t>
-  </si>
-  <si>
-    <t>90∘</t>
-  </si>
-  <si>
-    <t>180∘</t>
-  </si>
-  <si>
     <t>प्रत्यावर्ती धारा को मापने वाले मीटर (AC Ammeter) किस प्रभाव पर आधारित होते हैं?</t>
   </si>
   <si>
@@ -227,18 +143,6 @@
     <t>एक अपचायी (Step-down) ट्रान्सफॉर्मर में क्या होता है?</t>
   </si>
   <si>
-    <t>Vs​&gt;Vp​</t>
-  </si>
-  <si>
-    <t>Ns​&gt;Np​</t>
-  </si>
-  <si>
-    <t>Vs​&lt;Vp​</t>
-  </si>
-  <si>
-    <t>Is​&lt;Ip​</t>
-  </si>
-  <si>
     <t>प्रतिबाधा (Impedance) और प्रतिघात (Reactance) का SI मात्रक क्या है?</t>
   </si>
   <si>
@@ -254,18 +158,6 @@
     <t>किसी LCR परिपथ में गुणवत्ता गुणांक (Q-factor) की परिभाषा क्या है?</t>
   </si>
   <si>
-    <t>Rω0​L​</t>
-  </si>
-  <si>
-    <t>ω0​LR​</t>
-  </si>
-  <si>
-    <t>LRω0​​</t>
-  </si>
-  <si>
-    <t>यदि AC वोल्टेज समीकरण V=2002​sin(100πt) है, तो इसका वर्ग माध्य मूल (RMS) वोल्टेज कितना होगा?</t>
-  </si>
-  <si>
     <t>200 V</t>
   </si>
   <si>
@@ -309,6 +201,117 @@
   </si>
   <si>
     <t>एक शुद्ध प्रतिरोधक (Purely Resistive) AC परिपथ में शक्ति गुणांक (Power factor) का मान कितना होता है?</t>
+  </si>
+  <si>
+    <t>प्रत्यावर्ती धारा के शिखर मान (I₀) और वर्ग माध्य मूल मान (Irms) में क्या संबंध होता है?</t>
+  </si>
+  <si>
+    <t>Irms = I₀ / √2</t>
+  </si>
+  <si>
+    <t>Irms = √2 × I₀</t>
+  </si>
+  <si>
+    <t>Irms = 2 × I₀</t>
+  </si>
+  <si>
+    <t>Irms = I₀ / 2</t>
+  </si>
+  <si>
+    <t>I₀ / √2</t>
+  </si>
+  <si>
+    <t>धारा वोल्टेज से 90° आगे होती है</t>
+  </si>
+  <si>
+    <t>वोल्टेज धारा से 90° आगे होता है</t>
+  </si>
+  <si>
+    <t>कलान्तर 180° होता है</t>
+  </si>
+  <si>
+    <t>प्रेरणिक प्रतिघात (Inductive Reactance, XL) का सूत्र क्या है?</t>
+  </si>
+  <si>
+    <t>ω / L</t>
+  </si>
+  <si>
+    <t>1 / (ωL)</t>
+  </si>
+  <si>
+    <t>L / ω</t>
+  </si>
+  <si>
+    <t>दिष्ट धारा (DC) के लिए एक संधारित्र (Capacitor) का प्रतिघात (XC) कितना होता है?</t>
+  </si>
+  <si>
+    <t>XL + XC</t>
+  </si>
+  <si>
+    <t>श्रेणी LCR परिपथ की अनुनादी आवृत्ति (fr) का सूत्र क्या होता है?</t>
+  </si>
+  <si>
+    <t>1 / (2π√(LC))</t>
+  </si>
+  <si>
+    <t>2π / √(LC)</t>
+  </si>
+  <si>
+    <t>√(LC) / 2π</t>
+  </si>
+  <si>
+    <t>1 / (LC)</t>
+  </si>
+  <si>
+    <t>शक्ति गुणांक (Power Factor, cosφ) का अधिकतम मान कितना हो सकता है?</t>
+  </si>
+  <si>
+    <t>√2</t>
+  </si>
+  <si>
+    <t>Vrms × Irms</t>
+  </si>
+  <si>
+    <t>(1/2) Vrms × Irms</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>45°</t>
+  </si>
+  <si>
+    <t>90°</t>
+  </si>
+  <si>
+    <t>180°</t>
+  </si>
+  <si>
+    <t>Vs &gt; Vp</t>
+  </si>
+  <si>
+    <t>Ns &gt; Np</t>
+  </si>
+  <si>
+    <t>Vs &lt; Vp</t>
+  </si>
+  <si>
+    <t>Is &lt; Ip</t>
+  </si>
+  <si>
+    <t>(ω₀L) / R</t>
+  </si>
+  <si>
+    <t>R / (ω₀L)</t>
+  </si>
+  <si>
+    <t>ω₀ / (LR)</t>
+  </si>
+  <si>
+    <t>(LR) / ω₀</t>
+  </si>
+  <si>
+    <t>यदि AC वोल्टेज समीकरण V = 200√2 sin(100πt) है, तो इसका वर्ग माध्य मूल (RMS) वोल्टेज कितना होगा?</t>
   </si>
 </sst>
 </file>
@@ -709,19 +712,19 @@
     </row>
     <row r="3" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>7</v>
@@ -729,19 +732,19 @@
     </row>
     <row r="4" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>8</v>
@@ -749,19 +752,19 @@
     </row>
     <row r="5" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>7</v>
@@ -769,19 +772,19 @@
     </row>
     <row r="6" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>8</v>
@@ -789,19 +792,19 @@
     </row>
     <row r="7" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>8</v>
@@ -809,19 +812,19 @@
     </row>
     <row r="8" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>6</v>
@@ -829,19 +832,19 @@
     </row>
     <row r="9" spans="1:6" ht="89" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>7</v>
@@ -849,7 +852,7 @@
     </row>
     <row r="10" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="B10" s="3">
         <v>0</v>
@@ -858,10 +861,10 @@
         <v>1</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>6</v>
@@ -869,19 +872,19 @@
     </row>
     <row r="11" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>8</v>
@@ -889,19 +892,19 @@
     </row>
     <row r="12" spans="1:6" ht="176.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>8</v>
@@ -909,19 +912,19 @@
     </row>
     <row r="13" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>8</v>
@@ -929,19 +932,19 @@
     </row>
     <row r="14" spans="1:6" ht="64" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>6</v>
@@ -949,19 +952,19 @@
     </row>
     <row r="15" spans="1:6" ht="89" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>8</v>
@@ -969,19 +972,19 @@
     </row>
     <row r="16" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>8</v>
@@ -989,39 +992,39 @@
     </row>
     <row r="17" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>7</v>
@@ -1029,19 +1032,19 @@
     </row>
     <row r="19" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>6</v>
@@ -1049,19 +1052,19 @@
     </row>
     <row r="20" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>6</v>
@@ -1069,7 +1072,7 @@
     </row>
     <row r="21" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="B21" s="3">
         <v>0</v>

--- a/questions_12.xlsx
+++ b/questions_12.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="86">
   <si>
     <t>question</t>
   </si>
@@ -53,231 +53,6 @@
     <t>C</t>
   </si>
   <si>
-    <t>हेनरी</t>
-  </si>
-  <si>
-    <t>भारत में घरों में आपूर्ति की जाने वाली प्रत्यावर्ती धारा (AC) की आवृत्ति कितनी होती है?</t>
-  </si>
-  <si>
-    <t>60 Hz</t>
-  </si>
-  <si>
-    <t>50 Hz</t>
-  </si>
-  <si>
-    <t>100 Hz</t>
-  </si>
-  <si>
-    <t>0 Hz</t>
-  </si>
-  <si>
-    <t>एक पूरे चक्र (Full cycle) में प्रत्यावर्ती धारा का औसत मान (Average value) कितना होता है?</t>
-  </si>
-  <si>
-    <t>शिखर मान के बराबर</t>
-  </si>
-  <si>
-    <t>अनंत</t>
-  </si>
-  <si>
-    <t>शून्य</t>
-  </si>
-  <si>
-    <t>केवल धारिता (Capacitor) वाले AC परिपथ में धारा और वोल्टेज के बीच कलान्तर कितना होता है?</t>
-  </si>
-  <si>
-    <t>दोनों समान कला में होते हैं</t>
-  </si>
-  <si>
-    <t>ωL</t>
-  </si>
-  <si>
-    <t>1 ओम</t>
-  </si>
-  <si>
-    <t>आवृत्ति पर निर्भर</t>
-  </si>
-  <si>
-    <t>श्रेणी LCR परिपथ में अनुनाद (Resonance) की स्थिति में परिपथ की प्रतिबाधा (Impedance, Z) किसके बराबर होती है?</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>शुद्ध प्रेरकत्व (Pure Inductance) वाले AC परिपथ में क्षय होने वाली औसत शक्ति कितनी होती है?</t>
-  </si>
-  <si>
-    <t>वाटहीन धारा (Wattless current) प्रवाहित होने के लिए धारा और वोल्टेज के बीच कलान्तर कितना होना चाहिए?</t>
-  </si>
-  <si>
-    <t>प्रत्यावर्ती धारा को मापने वाले मीटर (AC Ammeter) किस प्रभाव पर आधारित होते हैं?</t>
-  </si>
-  <si>
-    <t>चुम्बकीय प्रभाव</t>
-  </si>
-  <si>
-    <t>रासायनिक प्रभाव</t>
-  </si>
-  <si>
-    <t>ऊष्मीय प्रभाव (तप्त तार सिद्धांत)</t>
-  </si>
-  <si>
-    <t>स्थिरवैद्युत प्रभाव</t>
-  </si>
-  <si>
-    <t>ट्रान्सफॉर्मर किस सिद्धांत पर कार्य करता है?</t>
-  </si>
-  <si>
-    <t>स्वप्रेरण</t>
-  </si>
-  <si>
-    <t>पारस्परिक प्रेरण (Mutual Induction)</t>
-  </si>
-  <si>
-    <t>भंवर धारा प्रभाव</t>
-  </si>
-  <si>
-    <t>सीबेक प्रभाव</t>
-  </si>
-  <si>
-    <t>एक अपचायी (Step-down) ट्रान्सफॉर्मर में क्या होता है?</t>
-  </si>
-  <si>
-    <t>प्रतिबाधा (Impedance) और प्रतिघात (Reactance) का SI मात्रक क्या है?</t>
-  </si>
-  <si>
-    <t>फैराड</t>
-  </si>
-  <si>
-    <t>ओम</t>
-  </si>
-  <si>
-    <t>वाट</t>
-  </si>
-  <si>
-    <t>किसी LCR परिपथ में गुणवत्ता गुणांक (Q-factor) की परिभाषा क्या है?</t>
-  </si>
-  <si>
-    <t>200 V</t>
-  </si>
-  <si>
-    <t>100 V</t>
-  </si>
-  <si>
-    <t>282.8 V</t>
-  </si>
-  <si>
-    <t>400 V</t>
-  </si>
-  <si>
-    <t>प्रत्यावर्ती धारा को दिष्ट धारा (DC) में परिवर्तित करने वाली युक्ति को क्या कहते हैं?</t>
-  </si>
-  <si>
-    <t>इन्वर्टर</t>
-  </si>
-  <si>
-    <t>दिष्टकारी (Rectifier)</t>
-  </si>
-  <si>
-    <t>ट्रान्सफॉर्मर</t>
-  </si>
-  <si>
-    <t>प्रेरक कुण्डली</t>
-  </si>
-  <si>
-    <t>चोक कुण्डली (Choke Coil) का उपयोग AC परिपथ में किसके लिए किया जाता है?</t>
-  </si>
-  <si>
-    <t>धारा बढ़ाने के लिए</t>
-  </si>
-  <si>
-    <t>ऊर्जा हानि किए बिना धारा नियंत्रित करने के लिए</t>
-  </si>
-  <si>
-    <t>वोल्टेज बढ़ाने के लिए</t>
-  </si>
-  <si>
-    <t>आवृत्ति बदलने के लिए</t>
-  </si>
-  <si>
-    <t>एक शुद्ध प्रतिरोधक (Purely Resistive) AC परिपथ में शक्ति गुणांक (Power factor) का मान कितना होता है?</t>
-  </si>
-  <si>
-    <t>प्रत्यावर्ती धारा के शिखर मान (I₀) और वर्ग माध्य मूल मान (Irms) में क्या संबंध होता है?</t>
-  </si>
-  <si>
-    <t>Irms = I₀ / √2</t>
-  </si>
-  <si>
-    <t>Irms = √2 × I₀</t>
-  </si>
-  <si>
-    <t>Irms = 2 × I₀</t>
-  </si>
-  <si>
-    <t>Irms = I₀ / 2</t>
-  </si>
-  <si>
-    <t>I₀ / √2</t>
-  </si>
-  <si>
-    <t>धारा वोल्टेज से 90° आगे होती है</t>
-  </si>
-  <si>
-    <t>वोल्टेज धारा से 90° आगे होता है</t>
-  </si>
-  <si>
-    <t>कलान्तर 180° होता है</t>
-  </si>
-  <si>
-    <t>प्रेरणिक प्रतिघात (Inductive Reactance, XL) का सूत्र क्या है?</t>
-  </si>
-  <si>
-    <t>ω / L</t>
-  </si>
-  <si>
-    <t>1 / (ωL)</t>
-  </si>
-  <si>
-    <t>L / ω</t>
-  </si>
-  <si>
-    <t>दिष्ट धारा (DC) के लिए एक संधारित्र (Capacitor) का प्रतिघात (XC) कितना होता है?</t>
-  </si>
-  <si>
-    <t>XL + XC</t>
-  </si>
-  <si>
-    <t>श्रेणी LCR परिपथ की अनुनादी आवृत्ति (fr) का सूत्र क्या होता है?</t>
-  </si>
-  <si>
-    <t>1 / (2π√(LC))</t>
-  </si>
-  <si>
-    <t>2π / √(LC)</t>
-  </si>
-  <si>
-    <t>√(LC) / 2π</t>
-  </si>
-  <si>
-    <t>1 / (LC)</t>
-  </si>
-  <si>
-    <t>शक्ति गुणांक (Power Factor, cosφ) का अधिकतम मान कितना हो सकता है?</t>
-  </si>
-  <si>
-    <t>√2</t>
-  </si>
-  <si>
-    <t>Vrms × Irms</t>
-  </si>
-  <si>
-    <t>(1/2) Vrms × Irms</t>
-  </si>
-  <si>
-    <t>0°</t>
-  </si>
-  <si>
     <t>45°</t>
   </si>
   <si>
@@ -287,31 +62,226 @@
     <t>180°</t>
   </si>
   <si>
-    <t>Vs &gt; Vp</t>
-  </si>
-  <si>
-    <t>Ns &gt; Np</t>
-  </si>
-  <si>
-    <t>Vs &lt; Vp</t>
-  </si>
-  <si>
-    <t>Is &lt; Ip</t>
-  </si>
-  <si>
-    <t>(ω₀L) / R</t>
-  </si>
-  <si>
-    <t>R / (ω₀L)</t>
-  </si>
-  <si>
-    <t>ω₀ / (LR)</t>
-  </si>
-  <si>
-    <t>(LR) / ω₀</t>
-  </si>
-  <si>
-    <t>यदि AC वोल्टेज समीकरण V = 200√2 sin(100πt) है, तो इसका वर्ग माध्य मूल (RMS) वोल्टेज कितना होगा?</t>
+    <t>विद्युत चुम्बकीय तरंगों की उत्पत्ति का मुख्य स्रोत क्या है?</t>
+  </si>
+  <si>
+    <t>स्थिर आवेश</t>
+  </si>
+  <si>
+    <t>एकसमान वेग से गतिमान आवेश</t>
+  </si>
+  <si>
+    <t>त्वरित आवेश</t>
+  </si>
+  <si>
+    <t>अनावेशित कण</t>
+  </si>
+  <si>
+    <t>मैक्सवेल के अनुसार विस्थापन धारा (Displacement Current) का सही सूत्र क्या है?</t>
+  </si>
+  <si>
+    <t>ε₀ (dΦE/dt)</t>
+  </si>
+  <si>
+    <t>μ₀ (dΦE/dt)</t>
+  </si>
+  <si>
+    <t>(1/ε₀) (dΦE/dt)</t>
+  </si>
+  <si>
+    <t>ε₀ (dΦB/dt)</t>
+  </si>
+  <si>
+    <t>निर्वात में विद्युत चुम्बकीय तरंगों की चाल (c) का सूत्र क्या होता है?</t>
+  </si>
+  <si>
+    <t>√(μ₀ε₀)</t>
+  </si>
+  <si>
+    <t>1 / √(μ₀ε₀)</t>
+  </si>
+  <si>
+    <t>μ₀ / ε₀</t>
+  </si>
+  <si>
+    <t>ε₀ / μ₀</t>
+  </si>
+  <si>
+    <t>विद्युत चुम्बकीय तरंगों की प्रकृति कैसी होती है?</t>
+  </si>
+  <si>
+    <t>अनुदैर्ध्य (Longitudinal)</t>
+  </si>
+  <si>
+    <t>अनुप्रस्थ (Transverse)</t>
+  </si>
+  <si>
+    <t>यांत्रिक (Mechanical)</t>
+  </si>
+  <si>
+    <t>दोनों अनुदैर्ध्य एवं अनुप्रस्थ</t>
+  </si>
+  <si>
+    <t>किसी विद्युत चुम्बकीय तरंग में संचरण की दिशा किसके अनुदिश होती है?</t>
+  </si>
+  <si>
+    <t>विद्युत क्षेत्र E के</t>
+  </si>
+  <si>
+    <t>चुम्बकीय क्षेत्र B के</t>
+  </si>
+  <si>
+    <t>E × B के</t>
+  </si>
+  <si>
+    <t>B × E के</t>
+  </si>
+  <si>
+    <t>विद्युत चुम्बकीय तरंग में विद्युत क्षेत्र (E₀) और चुम्बकीय क्षेत्र (B₀) के आयामों का अनुपात (E₀/B₀) किसके बराबर होता है?</t>
+  </si>
+  <si>
+    <t>प्रकाश की चाल (c)</t>
+  </si>
+  <si>
+    <t>1/c</t>
+  </si>
+  <si>
+    <t>c²</t>
+  </si>
+  <si>
+    <t>1/c²</t>
+  </si>
+  <si>
+    <t>विद्युत चुम्बकीय तरंगों में विद्युत क्षेत्र सदिश और चुम्बकीय क्षेत्र सदिश के बीच कलान्तर कितना होता है?</t>
+  </si>
+  <si>
+    <t>0° (समान कला)</t>
+  </si>
+  <si>
+    <t>निम्नलिखित में से किसकी तरंगदैर्ध्य (Wavelength) सबसे कम तथा आवृत्ति सबसे अधिक होती है?</t>
+  </si>
+  <si>
+    <t>रेडियो तरंगें</t>
+  </si>
+  <si>
+    <t>पराबैंगनी किरणें</t>
+  </si>
+  <si>
+    <t>एक्स-किरणें</t>
+  </si>
+  <si>
+    <t>गामा किरणें</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>निम्नलिखित में से किन तरंगों को ऊष्मा तरंगें (Heat Waves) भी कहा जाता है?</t>
+  </si>
+  <si>
+    <t>अवरक्त किरणें (Infrared)</t>
+  </si>
+  <si>
+    <t>माइक्रोवेव</t>
+  </si>
+  <si>
+    <t>जल शोधक (Water Purifier) में जीवाणुओं को नष्ट करने के लिए किस विकिरण का उपयोग किया जाता है?</t>
+  </si>
+  <si>
+    <t>अवरक्त किरणें</t>
+  </si>
+  <si>
+    <t>पराबैंगनी किरणें (UV rays)</t>
+  </si>
+  <si>
+    <t>रडार प्रणाली (Radar system) और माइक्रोवेव ओवन में कौन-सी तरंगें प्रयुक्त होती हैं?</t>
+  </si>
+  <si>
+    <t>सूक्ष्म तरंगें (Microwaves)</t>
+  </si>
+  <si>
+    <t>क्रिस्टल (रवेदार पदार्थों) की आंतरिक संरचना ज्ञात करने के लिए किन किरणों का उपयोग किया जाता है?</t>
+  </si>
+  <si>
+    <t>दृश्य प्रकाश</t>
+  </si>
+  <si>
+    <t>कैंसर कोशिकाओं को नष्ट करने (रेडियोथेरेपी) के लिए मुख्य रूप से कौन-सी किरणें उपयोग में लाई जाती हैं?</t>
+  </si>
+  <si>
+    <t>सूक्ष्म तरंगें</t>
+  </si>
+  <si>
+    <t>यदि कोई विद्युत चुम्बकीय तरंग U ऊर्जा वहन करती है, तो निर्वात में उसका संवेग (p) कितना होगा?</t>
+  </si>
+  <si>
+    <t>p = U × c</t>
+  </si>
+  <si>
+    <t>p = U / c</t>
+  </si>
+  <si>
+    <t>p = U / c²</t>
+  </si>
+  <si>
+    <t>p = c / U</t>
+  </si>
+  <si>
+    <t>पौध-घर प्रभाव (Greenhouse effect) के लिए मुख्य रूप से कौन-सी विकिरण जिम्मेदार है?</t>
+  </si>
+  <si>
+    <t>निर्वात में सभी विद्युत चुम्बकीय तरंगों के लिए निम्नलिखित में से क्या समान रहता है?</t>
+  </si>
+  <si>
+    <t>आवृत्ति</t>
+  </si>
+  <si>
+    <t>तरंगदैर्ध्य</t>
+  </si>
+  <si>
+    <t>चाल (Speed)</t>
+  </si>
+  <si>
+    <t>आयाम</t>
+  </si>
+  <si>
+    <t>ओजोन परत सूर्य से आने वाले किस हानिकारक विकिरण को अवशोषित करती है?</t>
+  </si>
+  <si>
+    <t>विद्युत चुम्बकीय तरंग में कुल औसत ऊर्जा घनत्व किसके बराबर होता है?</t>
+  </si>
+  <si>
+    <t>ε₀E₀²</t>
+  </si>
+  <si>
+    <t>(1/2)ε₀E₀²</t>
+  </si>
+  <si>
+    <t>2ε₀E₀²</t>
+  </si>
+  <si>
+    <t>(1/4)ε₀E₀²</t>
+  </si>
+  <si>
+    <t>कोहरे और धुंध में फोटोग्राफी करने के लिए किन तरंगों का उपयोग किया जाता है?</t>
+  </si>
+  <si>
+    <t>नीले प्रकाश की तरंगें</t>
+  </si>
+  <si>
+    <t>तरंगदैर्ध्य के बढ़ते क्रम में सही विन्यास कौन-सा है?</t>
+  </si>
+  <si>
+    <t>गामा &lt; एक्स-किरणें &lt; पराबैंगनी &lt; रेडियो</t>
+  </si>
+  <si>
+    <t>रेडियो &lt; अवरक्त &lt; दृश्य &lt; गामा</t>
+  </si>
+  <si>
+    <t>पराबैंगनी &lt; गामा &lt; एक्स-किरणें &lt; रेडियो</t>
+  </si>
+  <si>
+    <t>एक्स-किरणें &lt; गामा &lt; रेडियो &lt; दृश्य</t>
   </si>
 </sst>
 </file>
@@ -376,16 +346,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -690,404 +657,404 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="76.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="76.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:6" ht="189" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="89" thickBot="1" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" s="3">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="176.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="64" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="89" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F15" s="2" t="s">
+    <row r="16" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" ht="89" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="3">
-        <v>0</v>
-      </c>
-      <c r="C21" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="D21" s="3">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3">
-        <v>-1</v>
+        <v>81</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/questions_12.xlsx
+++ b/questions_12.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="183">
   <si>
     <t>question</t>
   </si>
@@ -62,226 +62,517 @@
     <t>180°</t>
   </si>
   <si>
-    <t>विद्युत चुम्बकीय तरंगों की उत्पत्ति का मुख्य स्रोत क्या है?</t>
-  </si>
-  <si>
-    <t>स्थिर आवेश</t>
-  </si>
-  <si>
-    <t>एकसमान वेग से गतिमान आवेश</t>
-  </si>
-  <si>
-    <t>त्वरित आवेश</t>
-  </si>
-  <si>
-    <t>अनावेशित कण</t>
-  </si>
-  <si>
-    <t>मैक्सवेल के अनुसार विस्थापन धारा (Displacement Current) का सही सूत्र क्या है?</t>
-  </si>
-  <si>
-    <t>ε₀ (dΦE/dt)</t>
-  </si>
-  <si>
-    <t>μ₀ (dΦE/dt)</t>
-  </si>
-  <si>
-    <t>(1/ε₀) (dΦE/dt)</t>
-  </si>
-  <si>
-    <t>ε₀ (dΦB/dt)</t>
-  </si>
-  <si>
-    <t>निर्वात में विद्युत चुम्बकीय तरंगों की चाल (c) का सूत्र क्या होता है?</t>
-  </si>
-  <si>
-    <t>√(μ₀ε₀)</t>
-  </si>
-  <si>
-    <t>1 / √(μ₀ε₀)</t>
-  </si>
-  <si>
-    <t>μ₀ / ε₀</t>
-  </si>
-  <si>
-    <t>ε₀ / μ₀</t>
-  </si>
-  <si>
-    <t>विद्युत चुम्बकीय तरंगों की प्रकृति कैसी होती है?</t>
-  </si>
-  <si>
-    <t>अनुदैर्ध्य (Longitudinal)</t>
-  </si>
-  <si>
-    <t>अनुप्रस्थ (Transverse)</t>
-  </si>
-  <si>
-    <t>यांत्रिक (Mechanical)</t>
-  </si>
-  <si>
-    <t>दोनों अनुदैर्ध्य एवं अनुप्रस्थ</t>
-  </si>
-  <si>
-    <t>किसी विद्युत चुम्बकीय तरंग में संचरण की दिशा किसके अनुदिश होती है?</t>
-  </si>
-  <si>
-    <t>विद्युत क्षेत्र E के</t>
-  </si>
-  <si>
-    <t>चुम्बकीय क्षेत्र B के</t>
-  </si>
-  <si>
-    <t>E × B के</t>
-  </si>
-  <si>
-    <t>B × E के</t>
-  </si>
-  <si>
-    <t>विद्युत चुम्बकीय तरंग में विद्युत क्षेत्र (E₀) और चुम्बकीय क्षेत्र (B₀) के आयामों का अनुपात (E₀/B₀) किसके बराबर होता है?</t>
-  </si>
-  <si>
-    <t>प्रकाश की चाल (c)</t>
-  </si>
-  <si>
-    <t>1/c</t>
-  </si>
-  <si>
-    <t>c²</t>
-  </si>
-  <si>
-    <t>1/c²</t>
-  </si>
-  <si>
-    <t>विद्युत चुम्बकीय तरंगों में विद्युत क्षेत्र सदिश और चुम्बकीय क्षेत्र सदिश के बीच कलान्तर कितना होता है?</t>
-  </si>
-  <si>
-    <t>0° (समान कला)</t>
-  </si>
-  <si>
-    <t>निम्नलिखित में से किसकी तरंगदैर्ध्य (Wavelength) सबसे कम तथा आवृत्ति सबसे अधिक होती है?</t>
-  </si>
-  <si>
-    <t>रेडियो तरंगें</t>
-  </si>
-  <si>
-    <t>पराबैंगनी किरणें</t>
-  </si>
-  <si>
-    <t>एक्स-किरणें</t>
-  </si>
-  <si>
-    <t>गामा किरणें</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
-    <t>निम्नलिखित में से किन तरंगों को ऊष्मा तरंगें (Heat Waves) भी कहा जाता है?</t>
-  </si>
-  <si>
-    <t>अवरक्त किरणें (Infrared)</t>
-  </si>
-  <si>
-    <t>माइक्रोवेव</t>
-  </si>
-  <si>
-    <t>जल शोधक (Water Purifier) में जीवाणुओं को नष्ट करने के लिए किस विकिरण का उपयोग किया जाता है?</t>
-  </si>
-  <si>
-    <t>अवरक्त किरणें</t>
-  </si>
-  <si>
-    <t>पराबैंगनी किरणें (UV rays)</t>
-  </si>
-  <si>
-    <t>रडार प्रणाली (Radar system) और माइक्रोवेव ओवन में कौन-सी तरंगें प्रयुक्त होती हैं?</t>
-  </si>
-  <si>
-    <t>सूक्ष्म तरंगें (Microwaves)</t>
-  </si>
-  <si>
-    <t>क्रिस्टल (रवेदार पदार्थों) की आंतरिक संरचना ज्ञात करने के लिए किन किरणों का उपयोग किया जाता है?</t>
-  </si>
-  <si>
-    <t>दृश्य प्रकाश</t>
-  </si>
-  <si>
-    <t>कैंसर कोशिकाओं को नष्ट करने (रेडियोथेरेपी) के लिए मुख्य रूप से कौन-सी किरणें उपयोग में लाई जाती हैं?</t>
-  </si>
-  <si>
-    <t>सूक्ष्म तरंगें</t>
-  </si>
-  <si>
-    <t>यदि कोई विद्युत चुम्बकीय तरंग U ऊर्जा वहन करती है, तो निर्वात में उसका संवेग (p) कितना होगा?</t>
-  </si>
-  <si>
-    <t>p = U × c</t>
-  </si>
-  <si>
-    <t>p = U / c</t>
-  </si>
-  <si>
-    <t>p = U / c²</t>
-  </si>
-  <si>
-    <t>p = c / U</t>
-  </si>
-  <si>
-    <t>पौध-घर प्रभाव (Greenhouse effect) के लिए मुख्य रूप से कौन-सी विकिरण जिम्मेदार है?</t>
-  </si>
-  <si>
-    <t>निर्वात में सभी विद्युत चुम्बकीय तरंगों के लिए निम्नलिखित में से क्या समान रहता है?</t>
-  </si>
-  <si>
     <t>आवृत्ति</t>
   </si>
   <si>
     <t>तरंगदैर्ध्य</t>
   </si>
   <si>
-    <t>चाल (Speed)</t>
-  </si>
-  <si>
     <t>आयाम</t>
   </si>
   <si>
-    <t>ओजोन परत सूर्य से आने वाले किस हानिकारक विकिरण को अवशोषित करती है?</t>
-  </si>
-  <si>
-    <t>विद्युत चुम्बकीय तरंग में कुल औसत ऊर्जा घनत्व किसके बराबर होता है?</t>
-  </si>
-  <si>
-    <t>ε₀E₀²</t>
-  </si>
-  <si>
-    <t>(1/2)ε₀E₀²</t>
-  </si>
-  <si>
-    <t>2ε₀E₀²</t>
-  </si>
-  <si>
-    <t>(1/4)ε₀E₀²</t>
-  </si>
-  <si>
-    <t>कोहरे और धुंध में फोटोग्राफी करने के लिए किन तरंगों का उपयोग किया जाता है?</t>
-  </si>
-  <si>
-    <t>नीले प्रकाश की तरंगें</t>
-  </si>
-  <si>
-    <t>तरंगदैर्ध्य के बढ़ते क्रम में सही विन्यास कौन-सा है?</t>
-  </si>
-  <si>
-    <t>गामा &lt; एक्स-किरणें &lt; पराबैंगनी &lt; रेडियो</t>
-  </si>
-  <si>
-    <t>रेडियो &lt; अवरक्त &lt; दृश्य &lt; गामा</t>
-  </si>
-  <si>
-    <t>पराबैंगनी &lt; गामा &lt; एक्स-किरणें &lt; रेडियो</t>
-  </si>
-  <si>
-    <t>एक्स-किरणें &lt; गामा &lt; रेडियो &lt; दृश्य</t>
+    <t>प्रकाश के परावर्तन के नियमानुसार आपतन कोण (i) और परावर्तन कोण (r) में क्या संबंध होता है?</t>
+  </si>
+  <si>
+    <t>i &gt; r</t>
+  </si>
+  <si>
+    <t>i &lt; r</t>
+  </si>
+  <si>
+    <t>i = r</t>
+  </si>
+  <si>
+    <t>i + r = 90°</t>
+  </si>
+  <si>
+    <t>समतल दर्पण की फोकस दूरी कितनी होती है?</t>
+  </si>
+  <si>
+    <t>शून्य</t>
+  </si>
+  <si>
+    <t>अनंत</t>
+  </si>
+  <si>
+    <t>25 cm</t>
+  </si>
+  <si>
+    <t>-25 cm</t>
+  </si>
+  <si>
+    <t>समतल दर्पण द्वारा बना प्रतिबिम्ब कैसा होता है?</t>
+  </si>
+  <si>
+    <t>वास्तविक और उल्टा</t>
+  </si>
+  <si>
+    <t>आभासी और सीधा</t>
+  </si>
+  <si>
+    <t>वास्तविक और सीधा</t>
+  </si>
+  <si>
+    <t>आभासी और उल्टा</t>
+  </si>
+  <si>
+    <t>यदि कोई व्यक्ति समतल दर्पण की ओर v वेग से चल रहा है, तो उसका प्रतिबिम्ब उसकी ओर किस वेग से आता हुआ प्रतीत होगा?</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>2v</t>
+  </si>
+  <si>
+    <t>v/2</t>
+  </si>
+  <si>
+    <t>गोलीय दर्पण की फोकस दूरी (f) और वक्रता त्रिज्या (R) में क्या संबंध होता है?</t>
+  </si>
+  <si>
+    <t>f = 2R</t>
+  </si>
+  <si>
+    <t>f = R/2</t>
+  </si>
+  <si>
+    <t>f = R</t>
+  </si>
+  <si>
+    <t>f = 1/R</t>
+  </si>
+  <si>
+    <t>वाहनों में पीछे का दृश्य देखने (Rear-view mirror) के लिए किस दर्पण का उपयोग किया जाता है?</t>
+  </si>
+  <si>
+    <t>अवतल दर्पण</t>
+  </si>
+  <si>
+    <t>उत्तल दर्पण</t>
+  </si>
+  <si>
+    <t>समतल दर्पण</t>
+  </si>
+  <si>
+    <t>परवलयाकार दर्पण</t>
+  </si>
+  <si>
+    <t>दंत चिकित्सक (Dentist) मरीजों के दांतों का बड़ा प्रतिबिम्ब देखने के लिए किस दर्पण का उपयोग करते हैं?</t>
+  </si>
+  <si>
+    <t>बेलनाकार दर्पण</t>
+  </si>
+  <si>
+    <t>जब वस्तु अवतल दर्पण के वक्रता केंद्र (C) पर रखी जाती है, तो प्रतिबिम्ब कहाँ बनता है?</t>
+  </si>
+  <si>
+    <t>फोकस पर</t>
+  </si>
+  <si>
+    <t>अनंत पर</t>
+  </si>
+  <si>
+    <t>वक्रता केंद्र पर</t>
+  </si>
+  <si>
+    <t>ध्रुव और फोकस के बीच</t>
+  </si>
+  <si>
+    <t>दर्पण सूत्र (Mirror Formula) निम्नलिखित में से कौन-सा है?</t>
+  </si>
+  <si>
+    <t>1/f = 1/v - 1/u</t>
+  </si>
+  <si>
+    <t>1/f = 1/v + 1/u</t>
+  </si>
+  <si>
+    <t>f = u + v</t>
+  </si>
+  <si>
+    <t>1/f = u/v</t>
+  </si>
+  <si>
+    <t>जब प्रकाश की किरण एक माध्यम से दूसरे माध्यम में प्रवेश करती है, तो कौन-सी राशि अपरिवर्तित रहती है?</t>
+  </si>
+  <si>
+    <t>चाल</t>
+  </si>
+  <si>
+    <t>स्नेल का अपवर्तन नियम किस समीकरण द्वारा व्यक्त किया जाता है?</t>
+  </si>
+  <si>
+    <t>sin i / sin r = μ</t>
+  </si>
+  <si>
+    <t>sin r / sin i = μ</t>
+  </si>
+  <si>
+    <t>sin i × sin r = μ</t>
+  </si>
+  <si>
+    <t>sin i + sin r = μ</t>
+  </si>
+  <si>
+    <t>निर्वात के सापेक्ष जल और काँच के अपवर्तनांक क्रमशः 4/3 और 3/2 हैं। काँच के सापेक्ष जल का अपवर्तनांक क्या होगा?</t>
+  </si>
+  <si>
+    <t>पूर्ण आंतरिक परावर्तन (TIR) की घटना तब होती है जब प्रकाश गमन करता है:</t>
+  </si>
+  <si>
+    <t>विरल से सघन माध्यम में</t>
+  </si>
+  <si>
+    <t>सघन से विरल माध्यम में</t>
+  </si>
+  <si>
+    <t>समान माध्यम में</t>
+  </si>
+  <si>
+    <t>निर्वात से सघन माध्यम में</t>
+  </si>
+  <si>
+    <t>जब आपतन कोण का मान क्रांतिक कोण (Critical Angle) के बराबर होता है, तो अपवर्तन कोण कितना होता है?</t>
+  </si>
+  <si>
+    <t>0°</t>
+  </si>
+  <si>
+    <t>प्रकाशिक तंतु (Optical Fibre) किस भौतिक सिद्धांत पर कार्य करता है?</t>
+  </si>
+  <si>
+    <t>विवर्तन</t>
+  </si>
+  <si>
+    <t>प्रकीर्णन</t>
+  </si>
+  <si>
+    <t>पूर्ण आंतरिक परावर्तन</t>
+  </si>
+  <si>
+    <t>व्यतिकरण</t>
+  </si>
+  <si>
+    <t>हीरे के अत्यधिक चमकने का मुख्य कारण क्या है?</t>
+  </si>
+  <si>
+    <t>उच्च अपवर्तनांक और छोटा क्रांतिक कोण</t>
+  </si>
+  <si>
+    <t>प्रकाश का अवशोषण</t>
+  </si>
+  <si>
+    <t>बड़ा क्रांतिक कोण</t>
+  </si>
+  <si>
+    <t>दर्पण की तरह परावर्तन</t>
+  </si>
+  <si>
+    <t>वास्तविक गहराई (h) और आभासी गहराई (h') में अपवर्तनांक (μ) के साथ क्या संबंध होता है?</t>
+  </si>
+  <si>
+    <t>h' = h × μ</t>
+  </si>
+  <si>
+    <t>h' = h / μ</t>
+  </si>
+  <si>
+    <t>h' = μ / h</t>
+  </si>
+  <si>
+    <t>h' = h - μ</t>
+  </si>
+  <si>
+    <t>किसी गोलीय अपवर्तक सतह के लिए अपवर्तन सूत्र क्या है?</t>
+  </si>
+  <si>
+    <t>μ₂/v - μ₁/u = (μ₂ - μ₁)/R</t>
+  </si>
+  <si>
+    <t>μ₁/v - μ₂/u = (μ₂ - μ₁)/R</t>
+  </si>
+  <si>
+    <t>μ₂/v + μ₁/u = (μ₂ - μ₁)/R</t>
+  </si>
+  <si>
+    <t>μ₂/v - μ₁/u = (μ₁ - μ₂)/R</t>
+  </si>
+  <si>
+    <t>पतले लेंस के लिए लेंस-निर्माता सूत्र (Lens Maker's Formula) क्या है?</t>
+  </si>
+  <si>
+    <t>1/f = (μ - 1)(1/R₁ - 1/R₂)</t>
+  </si>
+  <si>
+    <t>1/f = (μ + 1)(1/R₁ - 1/R₂)</t>
+  </si>
+  <si>
+    <t>1/f = (μ - 1)(1/R₁ + 1/R₂)</t>
+  </si>
+  <si>
+    <t>1/f = (1/μ)(1/R₁ - 1/R₂)</t>
+  </si>
+  <si>
+    <t>लेंस की क्षमता (Power of Lens) का SI मात्रक क्या है?</t>
+  </si>
+  <si>
+    <t>वाट</t>
+  </si>
+  <si>
+    <t>डायोप्टर</t>
+  </si>
+  <si>
+    <t>मीटर</t>
+  </si>
+  <si>
+    <t>जूल</t>
+  </si>
+  <si>
+    <t>+2 D और -4 D क्षमता वाले दो पतले लेंसों को संपर्क में रखने पर संयुक्त लेंस की क्षमता क्या होगी?</t>
+  </si>
+  <si>
+    <t>+6 D</t>
+  </si>
+  <si>
+    <t>-2 D</t>
+  </si>
+  <si>
+    <t>+2 D</t>
+  </si>
+  <si>
+    <t>-6 D</t>
+  </si>
+  <si>
+    <t>उत्तल लेंस को ऐसे द्रव में डुबोया जाता है जिसका अपवर्तनांक लेंस के पदार्थ के बराबर है। लेंस की फोकस दूरी हो जाएगी:</t>
+  </si>
+  <si>
+    <t>अपरिवर्तित</t>
+  </si>
+  <si>
+    <t>दोगुनी</t>
+  </si>
+  <si>
+    <t>किसी प्रिज़्म के पदार्थ के अपवर्तनांक का सूत्र क्या होता है?</t>
+  </si>
+  <si>
+    <t>sin((A + δm)/2) / sin(A/2)</t>
+  </si>
+  <si>
+    <t>sin(A/2) / sin((A + δm)/2)</t>
+  </si>
+  <si>
+    <t>sin(A + δm) / sin A</t>
+  </si>
+  <si>
+    <t>cos(A/2) / sin(δm/2)</t>
+  </si>
+  <si>
+    <t>श्वेत प्रकाश के प्रिज़्म से गुजरने पर किस रंग का विचलन सबसे अधिक होता है?</t>
+  </si>
+  <si>
+    <t>लाल</t>
+  </si>
+  <si>
+    <t>हरा</t>
+  </si>
+  <si>
+    <t>पीला</t>
+  </si>
+  <si>
+    <t>बैंगनी</t>
+  </si>
+  <si>
+    <t>श्वेत प्रकाश के किस रंग की चाल काँच में सबसे अधिक होती है?</t>
+  </si>
+  <si>
+    <t>नीला</t>
+  </si>
+  <si>
+    <t>आकाश का रंग नीला दिखाई देने का मुख्य कारण क्या है?</t>
+  </si>
+  <si>
+    <t>प्रकाश का अपवर्तन</t>
+  </si>
+  <si>
+    <t>प्रकाश का प्रकीर्णन</t>
+  </si>
+  <si>
+    <t>प्रकाश का विवर्तन</t>
+  </si>
+  <si>
+    <t>प्रकाश का परावर्तन</t>
+  </si>
+  <si>
+    <t>रैले (Rayleigh) के प्रकीर्णन नियमानुसार प्रकीर्णित प्रकाश की तीव्रता (I) तरंगदैर्ध्य (λ) के साथ कैसे संबंधित है?</t>
+  </si>
+  <si>
+    <t>I ∝ λ⁴</t>
+  </si>
+  <si>
+    <t>I ∝ 1/λ²</t>
+  </si>
+  <si>
+    <t>I ∝ 1/λ⁴</t>
+  </si>
+  <si>
+    <t>I ∝ 1/λ</t>
+  </si>
+  <si>
+    <t>सूर्योदय और सूर्यास्त के समय सूर्य का लाल दिखाई देना किस कारण से होता है?</t>
+  </si>
+  <si>
+    <t>प्रकाश का व्यतिकरण</t>
+  </si>
+  <si>
+    <t>प्रकाश का ध्रुवण</t>
+  </si>
+  <si>
+    <t>स्वस्थ मानव नेत्र के लिए स्पष्ट दृष्टि की न्यूनतम दूरी (Near Point) कितनी होती है?</t>
+  </si>
+  <si>
+    <t>25 m</t>
+  </si>
+  <si>
+    <t>2.5 cm</t>
+  </si>
+  <si>
+    <t>निकट दृष्टि दोष (Myopia) के निवारण के लिए किस लेंस का चश्मा प्रयोग किया जाता है?</t>
+  </si>
+  <si>
+    <t>उत्तल लेंस</t>
+  </si>
+  <si>
+    <t>अवतल लेंस</t>
+  </si>
+  <si>
+    <t>द्विफोकसी लेंस</t>
+  </si>
+  <si>
+    <t>बेलनाकार लेंस</t>
+  </si>
+  <si>
+    <t>दूर दृष्टि दोष (Hypermetropia) से पीड़ित व्यक्ति को किस प्रकार का लेंस दिया जाता है?</t>
+  </si>
+  <si>
+    <t>समतल लेंस</t>
+  </si>
+  <si>
+    <t>अवतलोत्तल लेंस</t>
+  </si>
+  <si>
+    <t>जरा दूरदृष्टिता (Presbyopia) को ठीक करने के लिए कौन-सा लेंस प्रयोग किया जाता है?</t>
+  </si>
+  <si>
+    <t>द्विफोकसी (Bifocal) लेंस</t>
+  </si>
+  <si>
+    <t>अबिंदुकता (Astigmatism) दोष के निवारण के लिए किस लेंस का उपयोग होता है?</t>
+  </si>
+  <si>
+    <t>संपर्क लेंस</t>
+  </si>
+  <si>
+    <t>एक सरल सूक्ष्मदर्शी (Simple Microscope) में कौन-सा लेंस प्रयुक्त होता है?</t>
+  </si>
+  <si>
+    <t>अधिक फोकस दूरी का उत्तल लेंस</t>
+  </si>
+  <si>
+    <t>कम फोकस दूरी का उत्तल लेंस</t>
+  </si>
+  <si>
+    <t>अधिक फोकस दूरी का अवतल लेंस</t>
+  </si>
+  <si>
+    <t>कम फोकस दूरी का अवतल लेंस</t>
+  </si>
+  <si>
+    <t>सामान्य समायोजन (अंतिम प्रतिबिम्ब अनंत पर) की स्थिति में सरल सूक्ष्मदर्शी की आवर्धन क्षमता क्या होती है?</t>
+  </si>
+  <si>
+    <t>1 + D/f</t>
+  </si>
+  <si>
+    <t>D/f</t>
+  </si>
+  <si>
+    <t>f/D</t>
+  </si>
+  <si>
+    <t>1 - D/f</t>
+  </si>
+  <si>
+    <t>संयुक्त सूक्ष्मदर्शी (Compound Microscope) में अभिदृश्यक (Objective) की फोकस दूरी नेत्रिका (Eyepiece) की तुलना में:</t>
+  </si>
+  <si>
+    <t>अधिक होती है</t>
+  </si>
+  <si>
+    <t>कम होती है</t>
+  </si>
+  <si>
+    <t>बराबर होती है</t>
+  </si>
+  <si>
+    <t>अनंत होती है</t>
+  </si>
+  <si>
+    <t>खगोलीय दूरदर्शी (Astronomical Telescope) में अंतिम प्रतिबिम्ब सीधा बनाने के लिए क्या आवश्यक है?</t>
+  </si>
+  <si>
+    <t>प्रतिलोमक लेंस</t>
+  </si>
+  <si>
+    <t>बड़ा अभिदृश्यक</t>
+  </si>
+  <si>
+    <t>सामान्य समायोजन में एक खगोलीय दूरदर्शी की नली की लम्बाई (Length of Tube) कितनी होती है?</t>
+  </si>
+  <si>
+    <t>fo - fe</t>
+  </si>
+  <si>
+    <t>fo + fe</t>
+  </si>
+  <si>
+    <t>fo × fe</t>
+  </si>
+  <si>
+    <t>fo / fe</t>
+  </si>
+  <si>
+    <t>एक खगोलीय दूरदर्शी के अभिदृश्यक लेंस का द्वारक (Aperture) बड़ा क्यों रखा जाता है?</t>
+  </si>
+  <si>
+    <t>आवर्धन क्षमता घटाने के लिए</t>
+  </si>
+  <si>
+    <t>विभेदन क्षमता और तीव्रता बढ़ाने के लिए</t>
+  </si>
+  <si>
+    <t>दूरदर्शी को हल्का बनाने के लिए</t>
+  </si>
+  <si>
+    <t>वर्ण विपथन दूर करने के लिए</t>
+  </si>
+  <si>
+    <t>परावर्ती दूरदर्शी (Cassegrain Telescope) में अभिदृश्यक के रूप में किसका उपयोग किया जाता है?</t>
+  </si>
+  <si>
+    <t>बड़े उत्तल लेंस का</t>
+  </si>
+  <si>
+    <t>बड़े अवतल दर्पण का</t>
+  </si>
+  <si>
+    <t>समतल दर्पण का</t>
+  </si>
+  <si>
+    <t>प्रिज्म का</t>
   </si>
 </sst>
 </file>
@@ -346,13 +637,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -634,7 +931,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:6" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -657,81 +954,81 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="76.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" ht="64" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="76.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="176.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="76.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>6</v>
@@ -739,322 +1036,722 @@
     </row>
     <row r="6" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="E8" s="2" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="89" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="176.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>45</v>
+        <v>64</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46243</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46273</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2</v>
+      </c>
+      <c r="E13" s="3">
+        <v>46054</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="176.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14" s="2" t="s">
+    <row r="16" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="76.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>46</v>
+        <v>93</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="89" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="89" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="101.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="89" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="114" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="189" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="164" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="139" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="126.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="151.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
